--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Syracuse_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Syracuse_20251031.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>105.63</t>
+          <t>140.84</t>
         </is>
       </c>
     </row>
